--- a/data/trans_orig/IP24_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>31292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72887</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86614</t>
+          <t>86215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65283</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79202</t>
+          <t>78801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142520</t>
+          <t>142323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161639</t>
+          <t>161711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>30565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>48052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59254</t>
+          <t>58941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>72196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61855</t>
+          <t>61826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>73848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125702</t>
+          <t>125307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142470</t>
+          <t>142794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44574</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44607</t>
+          <t>45252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72388</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85890</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121418</t>
+          <t>120301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138449</t>
+          <t>137988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42148</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55970</t>
+          <t>56357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>83257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110907</t>
+          <t>111493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139172</t>
+          <t>138820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158585</t>
+          <t>158672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146104</t>
+          <t>145717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165069</t>
+          <t>165329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291900</t>
+          <t>291314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318805</t>
+          <t>319550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26345</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42238</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>71946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61882</t>
+          <t>62338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>77895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91192</t>
+          <t>90682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106022</t>
+          <t>105764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>158557</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179995</t>
+          <t>180053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>46675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63461</t>
+          <t>63851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>43368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>56266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100863</t>
+          <t>99865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117763</t>
+          <t>117386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142048</t>
+          <t>143630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140142</t>
+          <t>140896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175897</t>
+          <t>177216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293717</t>
+          <t>294826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342875</t>
+          <t>343276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>457340</t>
+          <t>458557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>495354</t>
+          <t>493772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>507354</t>
+          <t>506035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>543109</t>
+          <t>542355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>977778</t>
+          <t>977377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1026936</t>
+          <t>1025827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79197</t>
+          <t>79092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135704</t>
+          <t>136570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152957</t>
+          <t>153043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>71905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84012</t>
+          <t>83397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73208</t>
+          <t>73391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>85002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150342</t>
+          <t>150016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166657</t>
+          <t>166364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>43636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58826</t>
+          <t>59509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71466</t>
+          <t>72057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>65889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77428</t>
+          <t>77401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129479</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146223</t>
+          <t>145232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>34594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>45750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68055</t>
+          <t>69123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95459</t>
+          <t>95710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151250</t>
+          <t>150516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170159</t>
+          <t>169730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177746</t>
+          <t>178616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196599</t>
+          <t>197212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333231</t>
+          <t>332980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360635</t>
+          <t>359567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63494</t>
+          <t>62707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107619</t>
+          <t>107568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123825</t>
+          <t>123397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107638</t>
+          <t>107849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>123111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221470</t>
+          <t>222257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244497</t>
+          <t>242397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56046</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66813</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>98035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111681</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121897</t>
+          <t>122154</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155632</t>
+          <t>156312</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100182</t>
+          <t>98367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132220</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228009</t>
+          <t>229971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275547</t>
+          <t>275209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>517259</t>
+          <t>516579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>550994</t>
+          <t>550737</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>575650</t>
+          <t>575819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>607688</t>
+          <t>609503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1105214</t>
+          <t>1105552</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1152752</t>
+          <t>1150790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>32790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51010</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59545</t>
+          <t>59997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>71999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>66790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80878</t>
+          <t>80711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131231</t>
+          <t>131941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>149451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>30642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75470</t>
+          <t>74385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88458</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>86466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99286</t>
+          <t>99180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>166194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183899</t>
+          <t>185141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68663</t>
+          <t>68336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103822</t>
+          <t>104212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118540</t>
+          <t>118300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>56831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65486</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91909</t>
+          <t>90008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165630</t>
+          <t>166076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185138</t>
+          <t>184728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170099</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187089</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341852</t>
+          <t>343753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368275</t>
+          <t>368675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37316</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57896</t>
+          <t>59375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101415</t>
+          <t>101645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116326</t>
+          <t>116385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112407</t>
+          <t>112785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126443</t>
+          <t>127133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219732</t>
+          <t>218253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240312</t>
+          <t>239364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33717</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>45669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60282</t>
+          <t>60479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86763</t>
+          <t>86776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102941</t>
+          <t>103273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166827</t>
+          <t>165744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102424</t>
+          <t>102484</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133593</t>
+          <t>133676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244326</t>
+          <t>244849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289216</t>
+          <t>292397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>503318</t>
+          <t>504401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537612</t>
+          <t>539811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>572553</t>
+          <t>572470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603722</t>
+          <t>603662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1087075</t>
+          <t>1083894</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1131965</t>
+          <t>1131442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48162</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84290</t>
+          <t>84970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103267</t>
+          <t>103636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>120436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192817</t>
+          <t>192716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>213139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25567</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>39586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68549</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82051</t>
+          <t>82016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76697</t>
+          <t>75650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87964</t>
+          <t>87390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149975</t>
+          <t>149573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166576</t>
+          <t>166847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47267</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47293</t>
+          <t>46583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>58271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88167</t>
+          <t>88665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103371</t>
+          <t>103157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56365</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137835</t>
+          <t>128830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96923</t>
+          <t>97663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192110</t>
+          <t>186384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79230</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160700</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160754</t>
+          <t>160923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181827</t>
+          <t>182500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>246759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336220</t>
+          <t>335480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>62160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85656</t>
+          <t>82708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93476</t>
+          <t>93354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>105980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101416</t>
+          <t>100061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139317</t>
+          <t>139032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>198942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240371</t>
+          <t>240584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61318</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>56360</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108941</t>
+          <t>109949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124756</t>
+          <t>125460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123778</t>
+          <t>124752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220506</t>
+          <t>219731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115595</t>
+          <t>114558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167274</t>
+          <t>166192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252011</t>
+          <t>248633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>377987</t>
+          <t>370675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>435321</t>
+          <t>436096</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>532049</t>
+          <t>531075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>577676</t>
+          <t>578758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629355</t>
+          <t>630392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1022790</t>
+          <t>1030102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1148766</t>
+          <t>1152144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
